--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="407">
   <si>
     <t/>
   </si>
@@ -760,7 +760,7 @@
     <t>20021571</t>
   </si>
   <si>
-    <t>ANLENE GOLD VAN 570G</t>
+    <t>ANLENE GOLD VAN 560G</t>
   </si>
   <si>
     <t>16</t>
@@ -1078,16 +1078,22 @@
     <t>DNCOW3+ VAN BOX  350</t>
   </si>
   <si>
+    <t>10010874</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 120</t>
+  </si>
+  <si>
     <t>20005712</t>
   </si>
   <si>
     <t>DNCOW 5+ VAN BOX 350</t>
   </si>
   <si>
-    <t>20138477</t>
-  </si>
-  <si>
-    <t>DANCOW CHO.CR 346.5G</t>
+    <t>10005338</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO BOX 195G</t>
   </si>
   <si>
     <t>10009494</t>
@@ -1154,18 +1160,6 @@
   </si>
   <si>
     <t>NTRILON 3 RYL VAN400</t>
-  </si>
-  <si>
-    <t>10010874</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 120</t>
-  </si>
-  <si>
-    <t>10005338</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO BOX 195G</t>
   </si>
   <si>
     <t>20057224</t>
@@ -1630,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4937,7 +4931,7 @@
         <v>17</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4951,10 +4945,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4962,19 +4956,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -4991,10 +4985,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5011,10 +5005,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5031,10 +5025,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5051,10 +5045,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5071,10 +5065,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5082,19 +5076,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5111,10 +5105,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5131,10 +5125,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5151,10 +5145,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5171,10 +5165,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5182,19 +5176,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5211,10 +5205,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5231,10 +5225,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5251,10 +5245,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5271,10 +5265,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5291,10 +5285,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5302,22 +5296,22 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5331,10 +5325,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>31</v>
@@ -5351,13 +5345,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5371,32 +5365,12 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F188" s="1" t="s">
         <v>5</v>
       </c>
     </row>
